--- a/public/Client-Intake-Template.xlsx
+++ b/public/Client-Intake-Template.xlsx
@@ -540,7 +540,6 @@
           <t>Your name</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -548,7 +547,6 @@
           <t>Agency name</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -556,7 +554,6 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -685,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -698,6 +695,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,6 +756,11 @@
           <t>Marketing Spend</t>
         </is>
       </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Active Clients</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -791,6 +794,9 @@
       </c>
       <c r="J3" s="5" t="n">
         <v>1500</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
